--- a/docs/StructureDefinition-respiratory-rate.xlsx
+++ b/docs/StructureDefinition-respiratory-rate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.6</t>
+    <t>0.5.8</t>
   </si>
   <si>
     <t>Name</t>

--- a/docs/StructureDefinition-respiratory-rate.xlsx
+++ b/docs/StructureDefinition-respiratory-rate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.8</t>
+    <t>0.5.9</t>
   </si>
   <si>
     <t>Name</t>

--- a/docs/StructureDefinition-respiratory-rate.xlsx
+++ b/docs/StructureDefinition-respiratory-rate.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3776" uniqueCount="662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3776" uniqueCount="661">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.12</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -484,25 +484,29 @@
     <t>A code representing the the type of device used for this observation.  Should only be used if not implicit in the code found in `Observation.code`.</t>
   </si>
   <si>
-    <t>Observation.extension:measurementDevice.id</t>
-  </si>
-  <si>
-    <t>Observation.extension.id</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
+    <t>Observation.extension:measurementDevice.id</t>
+  </si>
+  <si>
+    <t>Observation.extension.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
     <t>n/a</t>
   </si>
   <si>
@@ -552,7 +556,7 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>example</t>
@@ -571,10 +575,6 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">ext-1
-</t>
-  </si>
-  <si>
     <t>Observation.extension:measurementDevice.value[x]:valueCodeableConcept</t>
   </si>
   <si>
@@ -849,10 +849,6 @@
   </si>
   <si>
     <t>Observation.category.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
   </si>
   <si>
     <t>Observation.category:VSCat.extension</t>
@@ -3623,7 +3619,7 @@
         <v>82</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>144</v>
@@ -3649,10 +3645,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3675,13 +3671,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>95</v>
+        <v>153</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3732,7 +3728,7 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>81</v>
@@ -3741,7 +3737,7 @@
         <v>93</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>20</v>
@@ -3756,7 +3752,7 @@
         <v>20</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>20</v>
@@ -3767,10 +3763,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3841,7 +3837,7 @@
         <v>141</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>20</v>
@@ -3850,7 +3846,7 @@
         <v>142</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -3885,10 +3881,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3914,13 +3910,13 @@
         <v>107</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3928,7 +3924,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>20</v>
@@ -3970,7 +3966,7 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>93</v>
@@ -4005,10 +4001,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4031,13 +4027,13 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -4064,27 +4060,27 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -4093,7 +4089,7 @@
         <v>93</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>178</v>
+        <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>105</v>
@@ -4122,7 +4118,7 @@
         <v>179</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>180</v>
@@ -4147,13 +4143,13 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -4202,7 +4198,7 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -4211,7 +4207,7 @@
         <v>93</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>178</v>
+        <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>105</v>
@@ -4331,7 +4327,7 @@
         <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>144</v>
@@ -4360,7 +4356,7 @@
         <v>188</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4383,13 +4379,13 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>95</v>
+        <v>153</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4440,7 +4436,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4449,7 +4445,7 @@
         <v>93</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>20</v>
@@ -4464,7 +4460,7 @@
         <v>20</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>20</v>
@@ -4478,7 +4474,7 @@
         <v>189</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4549,7 +4545,7 @@
         <v>141</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>20</v>
@@ -4558,7 +4554,7 @@
         <v>142</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4596,7 +4592,7 @@
         <v>190</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4622,13 +4618,13 @@
         <v>107</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4678,7 +4674,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>93</v>
@@ -4716,7 +4712,7 @@
         <v>192</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4739,13 +4735,13 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4784,17 +4780,17 @@
         <v>20</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AC20" s="2"/>
       <c r="AD20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4803,7 +4799,7 @@
         <v>93</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>178</v>
+        <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>105</v>
@@ -4832,7 +4828,7 @@
         <v>193</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>180</v>
@@ -4857,13 +4853,13 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4912,7 +4908,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4921,7 +4917,7 @@
         <v>93</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>178</v>
+        <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>105</v>
@@ -5935,7 +5931,7 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>254</v>
@@ -6057,7 +6053,7 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>254</v>
@@ -6179,13 +6175,13 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>267</v>
+        <v>153</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6236,7 +6232,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6260,7 +6256,7 @@
         <v>20</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
@@ -6271,10 +6267,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6300,10 +6296,10 @@
         <v>138</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>211</v>
@@ -6347,7 +6343,7 @@
         <v>141</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>20</v>
@@ -6356,7 +6352,7 @@
         <v>142</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6380,7 +6376,7 @@
         <v>20</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>20</v>
@@ -6391,10 +6387,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6417,19 +6413,19 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -6478,7 +6474,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6499,10 +6495,10 @@
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
@@ -6513,10 +6509,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6539,13 +6535,13 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>267</v>
+        <v>153</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6596,7 +6592,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6620,7 +6616,7 @@
         <v>20</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
@@ -6631,10 +6627,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="B36" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6660,10 +6656,10 @@
         <v>138</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>211</v>
@@ -6707,7 +6703,7 @@
         <v>141</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>20</v>
@@ -6716,7 +6712,7 @@
         <v>142</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6740,7 +6736,7 @@
         <v>20</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
@@ -6751,10 +6747,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="B37" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6780,65 +6776,65 @@
         <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="S37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6859,10 +6855,10 @@
         <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
@@ -6873,10 +6869,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="B38" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6899,16 +6895,16 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>267</v>
+        <v>153</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6958,7 +6954,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6979,10 +6975,10 @@
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
@@ -6993,10 +6989,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="B39" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7022,63 +7018,63 @@
         <v>113</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF39" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="S39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7099,10 +7095,10 @@
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
@@ -7113,10 +7109,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="B40" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7139,17 +7135,17 @@
         <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>267</v>
+        <v>153</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -7198,7 +7194,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7219,10 +7215,10 @@
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>20</v>
@@ -7233,10 +7229,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="B41" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7259,19 +7255,19 @@
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -7320,7 +7316,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7341,10 +7337,10 @@
         <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>20</v>
@@ -7355,10 +7351,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="B42" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7381,19 +7377,19 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>267</v>
+        <v>153</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -7442,7 +7438,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7463,10 +7459,10 @@
         <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>20</v>
@@ -7477,14 +7473,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7503,19 +7499,19 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -7543,11 +7539,11 @@
         <v>181</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="Z43" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="Z43" t="s" s="2">
-        <v>347</v>
-      </c>
       <c r="AA43" t="s" s="2">
         <v>20</v>
       </c>
@@ -7564,7 +7560,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>93</v>
@@ -7579,30 +7575,30 @@
         <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AO43" t="s" s="2">
+      <c r="AP43" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>353</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7625,13 +7621,13 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>267</v>
+        <v>153</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7682,7 +7678,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7706,7 +7702,7 @@
         <v>20</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>20</v>
@@ -7717,10 +7713,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7746,10 +7742,10 @@
         <v>138</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>211</v>
@@ -7793,7 +7789,7 @@
         <v>141</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>20</v>
@@ -7802,7 +7798,7 @@
         <v>142</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7826,7 +7822,7 @@
         <v>20</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
@@ -7837,10 +7833,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7863,19 +7859,19 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -7912,7 +7908,7 @@
         <v>20</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AC46" s="2"/>
       <c r="AD46" t="s" s="2">
@@ -7922,7 +7918,7 @@
         <v>142</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7943,10 +7939,10 @@
         <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>20</v>
@@ -7957,13 +7953,13 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="C47" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>20</v>
@@ -7985,19 +7981,19 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -8046,7 +8042,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8067,10 +8063,10 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
@@ -8081,10 +8077,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="B48" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8107,13 +8103,13 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>267</v>
+        <v>153</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8164,7 +8160,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8188,7 +8184,7 @@
         <v>20</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>20</v>
@@ -8199,10 +8195,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="B49" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8228,10 +8224,10 @@
         <v>138</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>211</v>
@@ -8275,7 +8271,7 @@
         <v>141</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>20</v>
@@ -8284,7 +8280,7 @@
         <v>142</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8308,7 +8304,7 @@
         <v>20</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>20</v>
@@ -8319,10 +8315,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="B50" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8348,23 +8344,23 @@
         <v>107</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>20</v>
@@ -8406,7 +8402,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8427,10 +8423,10 @@
         <v>20</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>20</v>
@@ -8441,10 +8437,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B51" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8467,16 +8463,16 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>267</v>
+        <v>153</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8526,7 +8522,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8547,10 +8543,10 @@
         <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>20</v>
@@ -8561,10 +8557,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B52" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8590,21 +8586,21 @@
         <v>113</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>20</v>
@@ -8646,7 +8642,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8667,10 +8663,10 @@
         <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
@@ -8681,10 +8677,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="B53" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8707,17 +8703,17 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>267</v>
+        <v>153</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8766,7 +8762,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8787,10 +8783,10 @@
         <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
@@ -8801,10 +8797,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B54" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8827,19 +8823,19 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8888,7 +8884,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8909,10 +8905,10 @@
         <v>20</v>
       </c>
       <c r="AM54" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>20</v>
@@ -8923,10 +8919,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8949,19 +8945,19 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>267</v>
+        <v>153</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -9010,7 +9006,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9031,10 +9027,10 @@
         <v>20</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>20</v>
@@ -9045,10 +9041,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9071,19 +9067,19 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -9132,7 +9128,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9147,19 +9143,19 @@
         <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="AL56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM56" t="s" s="2">
+      <c r="AN56" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>20</v>
@@ -9167,10 +9163,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9193,16 +9189,16 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9252,7 +9248,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9273,13 +9269,13 @@
         <v>20</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>20</v>
@@ -9287,14 +9283,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9313,19 +9309,19 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
@@ -9374,7 +9370,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9389,19 +9385,19 @@
         <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AL58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>20</v>
@@ -9409,14 +9405,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9435,19 +9431,19 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="N59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -9496,7 +9492,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9505,25 +9501,25 @@
         <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AJ59" t="s" s="2">
+      <c r="AK59" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AK59" t="s" s="2">
+      <c r="AL59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="AL59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>20</v>
@@ -9531,10 +9527,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9557,16 +9553,16 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9616,7 +9612,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9637,13 +9633,13 @@
         <v>20</v>
       </c>
       <c r="AM60" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AN60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>20</v>
@@ -9651,10 +9647,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9677,17 +9673,17 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -9736,7 +9732,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9751,19 +9747,19 @@
         <v>105</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AL61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM61" t="s" s="2">
+      <c r="AN61" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AN61" t="s" s="2">
+      <c r="AO61" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>20</v>
@@ -9771,10 +9767,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9797,19 +9793,19 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M62" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -9846,17 +9842,17 @@
         <v>20</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AC62" s="2"/>
       <c r="AD62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9865,7 +9861,7 @@
         <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>105</v>
@@ -9874,30 +9870,30 @@
         <v>20</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AM62" t="s" s="2">
+      <c r="AN62" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="AN62" t="s" s="2">
+      <c r="AO62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP62" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>443</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C63" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="C63" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>20</v>
@@ -9919,19 +9915,19 @@
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N63" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M63" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -9980,7 +9976,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9989,7 +9985,7 @@
         <v>93</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>105</v>
@@ -9998,27 +9994,27 @@
         <v>20</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AM63" t="s" s="2">
+      <c r="AN63" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="AN63" t="s" s="2">
+      <c r="AO63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP63" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>443</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B64" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10041,13 +10037,13 @@
         <v>20</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>267</v>
+        <v>153</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10098,7 +10094,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10122,7 +10118,7 @@
         <v>20</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>20</v>
@@ -10133,10 +10129,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="B65" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10162,10 +10158,10 @@
         <v>138</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>211</v>
@@ -10209,7 +10205,7 @@
         <v>141</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>20</v>
@@ -10218,7 +10214,7 @@
         <v>142</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10242,7 +10238,7 @@
         <v>20</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>20</v>
@@ -10253,10 +10249,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B66" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10279,19 +10275,19 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="N66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -10340,7 +10336,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10361,10 +10357,10 @@
         <v>20</v>
       </c>
       <c r="AM66" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>20</v>
@@ -10375,10 +10371,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="B67" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10404,20 +10400,20 @@
         <v>113</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q67" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="P67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q67" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="R67" t="s" s="2">
         <v>20</v>
@@ -10441,28 +10437,28 @@
         <v>246</v>
       </c>
       <c r="Y67" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="Z67" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="Z67" t="s" s="2">
+      <c r="AA67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF67" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10483,10 +10479,10 @@
         <v>20</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>20</v>
@@ -10497,10 +10493,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="B68" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10523,17 +10519,17 @@
         <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>267</v>
+        <v>153</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -10582,7 +10578,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10603,10 +10599,10 @@
         <v>20</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>20</v>
@@ -10617,10 +10613,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10646,72 +10642,72 @@
         <v>107</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="S69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF69" t="s" s="2">
+      <c r="AG69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI69" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>105</v>
@@ -10723,10 +10719,10 @@
         <v>20</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>20</v>
@@ -10737,10 +10733,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="B70" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10766,65 +10762,65 @@
         <v>113</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="M70" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF70" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10845,10 +10841,10 @@
         <v>20</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>20</v>
@@ -10859,10 +10855,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10885,19 +10881,19 @@
         <v>20</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>20</v>
@@ -10925,37 +10921,37 @@
         <v>181</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="Z71" t="s" s="2">
+      <c r="AA71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI71" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>105</v>
@@ -10970,7 +10966,7 @@
         <v>136</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>20</v>
@@ -10981,14 +10977,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -11007,19 +11003,19 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="N72" t="s" s="2">
+      <c r="O72" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>20</v>
@@ -11048,7 +11044,7 @@
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>20</v>
@@ -11066,7 +11062,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11084,27 +11080,27 @@
         <v>20</v>
       </c>
       <c r="AL72" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AM72" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="AM72" t="s" s="2">
+      <c r="AN72" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="AN72" t="s" s="2">
+      <c r="AO72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>515</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11127,19 +11123,19 @@
         <v>20</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="N73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>521</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>20</v>
@@ -11188,7 +11184,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11209,10 +11205,10 @@
         <v>20</v>
       </c>
       <c r="AM73" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AN73" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>20</v>
@@ -11223,10 +11219,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11249,16 +11245,16 @@
         <v>20</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11284,14 +11280,14 @@
         <v>20</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y74" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="Z74" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="Z74" t="s" s="2">
-        <v>529</v>
-      </c>
       <c r="AA74" t="s" s="2">
         <v>20</v>
       </c>
@@ -11308,7 +11304,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11326,27 +11322,27 @@
         <v>20</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AN74" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="AN74" t="s" s="2">
+      <c r="AO74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>533</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11369,19 +11365,19 @@
         <v>20</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="N75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>20</v>
@@ -11410,7 +11406,7 @@
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>20</v>
@@ -11428,7 +11424,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11449,10 +11445,10 @@
         <v>20</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>20</v>
@@ -11463,10 +11459,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11489,16 +11485,16 @@
         <v>20</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11548,7 +11544,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11566,27 +11562,27 @@
         <v>20</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AM76" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="AM76" t="s" s="2">
+      <c r="AN76" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="AN76" t="s" s="2">
+      <c r="AO76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP76" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>550</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11609,16 +11605,16 @@
         <v>20</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11668,7 +11664,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11686,27 +11682,27 @@
         <v>20</v>
       </c>
       <c r="AL77" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AM77" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="AM77" t="s" s="2">
+      <c r="AN77" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="AN77" t="s" s="2">
+      <c r="AO77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP77" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>559</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11729,19 +11725,19 @@
         <v>20</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="N78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>20</v>
@@ -11790,7 +11786,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11802,19 +11798,19 @@
         <v>20</v>
       </c>
       <c r="AJ78" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM78" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="AK78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM78" t="s" s="2">
+      <c r="AN78" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>20</v>
@@ -11825,10 +11821,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11851,13 +11847,13 @@
         <v>20</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>267</v>
+        <v>153</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11908,7 +11904,7 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11932,7 +11928,7 @@
         <v>20</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>20</v>
@@ -11943,10 +11939,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11972,10 +11968,10 @@
         <v>138</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>211</v>
@@ -12028,7 +12024,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12052,7 +12048,7 @@
         <v>20</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>20</v>
@@ -12063,14 +12059,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -12092,10 +12088,10 @@
         <v>138</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>211</v>
@@ -12150,7 +12146,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12185,10 +12181,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12211,13 +12207,13 @@
         <v>20</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12268,7 +12264,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12277,7 +12273,7 @@
         <v>93</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>105</v>
@@ -12289,10 +12285,10 @@
         <v>20</v>
       </c>
       <c r="AM82" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AN82" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>20</v>
@@ -12303,10 +12299,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12329,13 +12325,13 @@
         <v>20</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12386,7 +12382,7 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12395,7 +12391,7 @@
         <v>93</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>105</v>
@@ -12407,10 +12403,10 @@
         <v>20</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>20</v>
@@ -12421,10 +12417,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12447,19 +12443,19 @@
         <v>20</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="N84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>20</v>
@@ -12487,11 +12483,11 @@
         <v>117</v>
       </c>
       <c r="Y84" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="Z84" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="Z84" t="s" s="2">
-        <v>593</v>
-      </c>
       <c r="AA84" t="s" s="2">
         <v>20</v>
       </c>
@@ -12508,7 +12504,7 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12526,13 +12522,13 @@
         <v>20</v>
       </c>
       <c r="AL84" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AM84" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="AM84" t="s" s="2">
-        <v>595</v>
-      </c>
       <c r="AN84" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>20</v>
@@ -12543,10 +12539,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12569,19 +12565,19 @@
         <v>20</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="N85" t="s" s="2">
+      <c r="O85" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>20</v>
@@ -12606,14 +12602,14 @@
         <v>20</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y85" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="Z85" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="Z85" t="s" s="2">
-        <v>602</v>
-      </c>
       <c r="AA85" t="s" s="2">
         <v>20</v>
       </c>
@@ -12630,7 +12626,7 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12648,13 +12644,13 @@
         <v>20</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AM85" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="AM85" t="s" s="2">
-        <v>595</v>
-      </c>
       <c r="AN85" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>20</v>
@@ -12665,10 +12661,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12691,17 +12687,17 @@
         <v>20</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="M86" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>20</v>
@@ -12750,7 +12746,7 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12774,7 +12770,7 @@
         <v>20</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>20</v>
@@ -12785,10 +12781,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12811,13 +12807,13 @@
         <v>20</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>267</v>
+        <v>153</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12868,7 +12864,7 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12889,10 +12885,10 @@
         <v>20</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>20</v>
@@ -12903,10 +12899,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12929,16 +12925,16 @@
         <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12988,7 +12984,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13009,10 +13005,10 @@
         <v>20</v>
       </c>
       <c r="AM88" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>20</v>
@@ -13023,10 +13019,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13049,16 +13045,16 @@
         <v>94</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="M89" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="N89" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13108,7 +13104,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13129,10 +13125,10 @@
         <v>20</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>20</v>
@@ -13143,10 +13139,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13169,19 +13165,19 @@
         <v>94</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="N90" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="M90" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="N90" t="s" s="2">
+      <c r="O90" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>20</v>
@@ -13230,7 +13226,7 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13242,19 +13238,19 @@
         <v>20</v>
       </c>
       <c r="AJ90" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM90" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="AK90" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM90" t="s" s="2">
+      <c r="AN90" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>20</v>
@@ -13265,10 +13261,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13291,13 +13287,13 @@
         <v>20</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>267</v>
+        <v>153</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13348,7 +13344,7 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13372,7 +13368,7 @@
         <v>20</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>20</v>
@@ -13383,10 +13379,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13412,10 +13408,10 @@
         <v>138</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>211</v>
@@ -13468,7 +13464,7 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13492,7 +13488,7 @@
         <v>20</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>20</v>
@@ -13503,14 +13499,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13532,10 +13528,10 @@
         <v>138</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>211</v>
@@ -13590,7 +13586,7 @@
         <v>20</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13625,10 +13621,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13651,19 +13647,19 @@
         <v>94</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="N94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>20</v>
@@ -13691,11 +13687,11 @@
         <v>181</v>
       </c>
       <c r="Y94" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="Z94" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="Z94" t="s" s="2">
-        <v>347</v>
-      </c>
       <c r="AA94" t="s" s="2">
         <v>20</v>
       </c>
@@ -13712,7 +13708,7 @@
         <v>20</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>93</v>
@@ -13730,16 +13726,16 @@
         <v>20</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AM94" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AN94" t="s" s="2">
+      <c r="AO94" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>20</v>
@@ -13747,10 +13743,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13773,19 +13769,19 @@
         <v>94</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="N95" t="s" s="2">
-        <v>646</v>
-      </c>
       <c r="O95" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>20</v>
@@ -13813,37 +13809,37 @@
         <v>181</v>
       </c>
       <c r="Y95" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="Z95" t="s" s="2">
         <v>647</v>
       </c>
-      <c r="Z95" t="s" s="2">
+      <c r="AA95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI95" t="s" s="2">
         <v>648</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="AG95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH95" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI95" t="s" s="2">
-        <v>649</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>105</v>
@@ -13852,27 +13848,27 @@
         <v>20</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="AM95" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AN95" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="AN95" t="s" s="2">
+      <c r="AO95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP95" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP95" t="s" s="2">
-        <v>443</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13895,19 +13891,19 @@
         <v>20</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>652</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>653</v>
       </c>
-      <c r="N96" t="s" s="2">
-        <v>654</v>
-      </c>
       <c r="O96" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>20</v>
@@ -13935,11 +13931,11 @@
         <v>181</v>
       </c>
       <c r="Y96" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="Z96" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="Z96" t="s" s="2">
-        <v>502</v>
-      </c>
       <c r="AA96" t="s" s="2">
         <v>20</v>
       </c>
@@ -13956,7 +13952,7 @@
         <v>20</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13965,7 +13961,7 @@
         <v>93</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>105</v>
@@ -13980,7 +13976,7 @@
         <v>136</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>20</v>
@@ -13991,14 +13987,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -14017,19 +14013,19 @@
         <v>20</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="N97" t="s" s="2">
+      <c r="O97" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>20</v>
@@ -14057,11 +14053,11 @@
         <v>181</v>
       </c>
       <c r="Y97" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="Z97" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="Z97" t="s" s="2">
-        <v>658</v>
-      </c>
       <c r="AA97" t="s" s="2">
         <v>20</v>
       </c>
@@ -14078,7 +14074,7 @@
         <v>20</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -14096,27 +14092,27 @@
         <v>20</v>
       </c>
       <c r="AL97" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AM97" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="AM97" t="s" s="2">
+      <c r="AN97" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="AN97" t="s" s="2">
+      <c r="AO97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP97" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>515</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14142,16 +14138,16 @@
         <v>20</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>660</v>
       </c>
-      <c r="M98" t="s" s="2">
-        <v>661</v>
-      </c>
       <c r="N98" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="O98" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>20</v>
@@ -14200,7 +14196,7 @@
         <v>20</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14221,10 +14217,10 @@
         <v>20</v>
       </c>
       <c r="AM98" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AN98" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>20</v>

--- a/docs/StructureDefinition-respiratory-rate.xlsx
+++ b/docs/StructureDefinition-respiratory-rate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
